--- a/stories/arbres/TREE-SAN-002.xlsx
+++ b/stories/arbres/TREE-SAN-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est l'heure du déjeuner. Nora a faim. Papa pose les assiettes. Maman apporte le pain. On mange assis à table, ensemble. Nora va choisir sa place. Les fesses sur la chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre près de papa, près de maman, ou sa petite chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora tire la chaise près de papa. La chaise fait un petit bruit. Elle pose les fesses sur la chaise. Elle est assise. Papa s'assoit aussi. Maman s'assoit en face. Ils sont ensemble à table. Nora prend sa cuillère. Elle reste assise.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nora va manger. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est assise. La table est stable. Papa, maman et Nora mangent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la soupe, le pain, ou le fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2203,7 +2250,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Papa souffle un peu sur la soupe. Nora reste assise. Elle mange à table, ensemble. La cuillère va, la cuillère vient. Maman dit : on est assis. C'est calme.</t>
+          <t>Papa souffle un peu sur la soupe. Nora reste assise. Elle mange à table, ensemble. La cuillère va, la cuillère vient. On est assis. C'est calme.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2341,6 +2388,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Papa souffle un peu sur la soupe. Nora reste assise. Elle mange à table, ensemble. La cuillère va, la cuillère vient.
+maman|On est assis. C'est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette bleue est devant Nora. Elle est assise à table. Ils mangent la soupe ensemble. Nora dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette rouge brille. Nora reste assise. À table, ensemble, la soupe est tiède. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette verte est ronde. Nora est assise. Ils mangent ensemble à table. Maman essuie une goutte.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maman casse le pain. Nora est assise. Elle attend, les fesses sur la chaise. Puis elle mange le pain à table, ensemble. Ça sent bon.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose le pain dans l'assiette bleue. Elle est assise à table, ensemble. Le pain croque.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4195,7 +4303,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>L'assiette rouge attend le pain. Nora reste assise. Ils mangent ensemble à table. Papa dit : bravo.</t>
+          <t>L'assiette rouge attend le pain. Nora reste assise. Ils mangent ensemble à table. Bravo.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4333,6 +4441,12 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette rouge attend le pain. Nora reste assise. Ils mangent ensemble à table.
+papa|Bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette verte est près de maman. Nora est assise. À table, ensemble, elle mange son morceau.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4843,7 +4972,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Papa coupe un petit bout de fromage. Nora est assise. Elle mange à table, ensemble. Le fromage est doux. Maman dit : on reste assis jusqu'à la fin.</t>
+          <t>Papa coupe un petit bout de fromage. Nora est assise. Elle mange à table, ensemble. Le fromage est doux. On reste assis jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4981,6 +5110,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Papa coupe un petit bout de fromage. Nora est assise. Elle mange à table, ensemble. Le fromage est doux.
+maman|On reste assis jusqu'à la fin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5302,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5469,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Le fromage est dans l'assiette bleue. Nora est assise à table. Ils mangent ensemble. Puis ils rangent.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5636,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5803,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette rouge sent le fromage. Nora reste assise. Ensemble, à table, c'est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5970,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5839,7 +5999,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>L'assiette verte attend. Nora est assise. Ils mangent ensemble à table. Nora dit : j'étais assise.</t>
+          <t>L'assiette verte attend. Nora est assise. Ils mangent ensemble à table. J'étais assise.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5977,6 +6137,12 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette verte attend. Nora est assise. Ils mangent ensemble à table.
+enfant-f|J'étais assise.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6305,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6472,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nora choisit la chaise près de maman. La nappe est douce. Elle s'assoit. Les fesses sur la chaise. Maman s'assoit à côté. Papa en face. Ils mangent ensemble à table. Nora tient sa fourchette. Elle reste assise.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6653,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est près de maman. Que fait-elle pour manger ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6826,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Près de maman, Nora est assise. La table les tient ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7017,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la soupe, le pain, ou le fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7184,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Maman goûte la soupe. Nora est assise à côté. Elle mange à table, ensemble. Une goutte tombe. Maman l'essuie. Nora reste sur sa chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7375,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7542,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette bleue fume un peu. Nora est assise à table, ensemble. Elle souffle.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7709,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7876,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette rouge est près de maman. Nora reste assise. Ils mangent ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8043,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8210,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette verte attend la cuillère. Nora est assise. Ensemble, à table, c'est bon.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8377,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8175,7 +8406,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Papa passe le panier. Nora, assise, prend un morceau. Elle mange le pain à table, ensemble. Maman dit : les fesses sur la chaise.</t>
+          <t>Papa passe le panier. Nora, assise, prend un morceau. Elle mange le pain à table, ensemble. Les fesses sur la chaise.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8313,6 +8544,12 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Papa passe le panier. Nora, assise, prend un morceau. Elle mange le pain à table, ensemble.
+maman|Les fesses sur la chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8736,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8903,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain est sur l'assiette bleue. Nora est assise à table. Ils mangent ensemble. Des miettes. On les ramasse.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9070,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9237,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette rouge a des miettes. Nora reste assise. Ensemble, à table, elle mange.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9404,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9571,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette verte est propre. Nora est assise. Ils mangent le pain ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9738,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9495,7 +9767,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Maman pose le fromage. Nora est assise. Elle attend son tour, à table, ensemble. Puis elle mange. Papa dit : on est tous assis.</t>
+          <t>Maman pose le fromage. Nora est assise. Elle attend son tour, à table, ensemble. Puis elle mange. On est tous assis.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9633,6 +9905,12 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maman pose le fromage. Nora est assise. Elle attend son tour, à table, ensemble. Puis elle mange.
+papa|On est tous assis.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10097,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10264,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette bleue a un petit bout. Nora est assise à table, ensemble. Elle dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10431,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10598,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette rouge sent bon. Nora reste assise. Ils mangent ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10765,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10932,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette verte est au milieu. Nora est assise. À table, ensemble, le repas se termine.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11099,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11128,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Nora a sa petite chaise, juste à sa taille. Elle s'assoit. Les fesses bien posées. Papa et maman s'assoient aussi. Ils mangent ensemble à table. Nora dit : je suis assise. Maman sourit.</t>
+          <t>Nora a sa petite chaise, juste à sa taille. Elle s'assoit. Les fesses bien posées. Papa et maman s'assoient aussi. Ils mangent ensemble à table. Je suis assise. Maman sourit.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11266,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a sa petite chaise, juste à sa taille. Elle s'assoit. Les fesses bien posées. Papa et maman s'assoient aussi. Ils mangent ensemble à table.
+enfant-f|Je suis assise. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11448,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a sa petite chaise. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11621,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|La petite chaise est stable. Nora est assise. Toute la famille est ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11812,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la soupe, le pain, ou le fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11979,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|La soupe arrive. Nora, sur sa petite chaise, reste assise. Elle mange à table, ensemble. La cuillère est à sa taille.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12170,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12337,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette bleue est petite aussi. Nora est assise à table. Ils mangent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12504,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12671,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette rouge va bien avec la chaise. Nora reste assise. Ensemble, à table, elle finit sa cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12838,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13005,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette verte est ronde. Nora est assise. Ils mangent ensemble à table. Papa range.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13172,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12827,7 +13201,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Nora, assise, rompt un peu de pain. Elle mange à table, ensemble. Sa petite chaise ne bouge pas. Maman dit : bien.</t>
+          <t>Nora, assise, rompt un peu de pain. Elle mange à table, ensemble. Sa petite chaise ne bouge pas. Bien.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12965,6 +13339,12 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nora, assise, rompt un peu de pain. Elle mange à table, ensemble. Sa petite chaise ne bouge pas.
+maman|Bien.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13531,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13698,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain rejoint l'assiette bleue. Nora est assise à table, ensemble. Une miette tombe. Elle la pose.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13865,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14032,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette rouge attend. Nora reste assise. Ils mangent le pain ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14199,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14366,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette verte a une miette. Nora est assise. À table, ensemble, c'est fini.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14533,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14700,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Papa glisse un bout de fromage. Nora est assise. Elle mange à table, ensemble. Elle reste jusqu'au bout, sur sa petite chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14891,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15058,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette bleue est vide, presque. Nora est assise à table. Ils étaient ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15225,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15392,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette rouge a encore une odeur. Nora reste assise. Ensemble, à table, elle dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15559,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15726,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|L'assiette verte rentre dans le placard. Nora était assise. Ils ont mangé ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15893,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15933,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-002.xlsx
+++ b/stories/arbres/TREE-SAN-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|C'est l'heure du déjeuner. Nora a faim. Papa pose les assiettes. Maman apporte le pain. On mange assis à table, ensemble. Nora va choisir sa place. Les fesses sur la chaise.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre près de papa, près de maman, ou sa petite chaise.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Nora tire la chaise près de papa. La chaise fait un petit bruit. Elle pose les fesses sur la chaise. Elle est assise. Papa s'assoit aussi. Maman s'assoit en face. Ils sont ensemble à table. Nora prend sa cuillère. Elle reste assise.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Nora va manger. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Nora est assise. La table est stable. Papa, maman et Nora mangent ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre la soupe, le pain, ou le fromage.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
 maman|On est assis. C'est calme.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|L'assiette bleue est devant Nora. Elle est assise à table. Ils mangent la soupe ensemble. Nora dit merci.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|L'assiette rouge brille. Nora reste assise. À table, ensemble, la soupe est tiède. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|L'assiette verte est ronde. Nora est assise. Ils mangent ensemble à table. Maman essuie une goutte.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Maman casse le pain. Nora est assise. Elle attend, les fesses sur la chaise. Puis elle mange le pain à table, ensemble. Ça sent bon.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Nora pose le pain dans l'assiette bleue. Elle est assise à table, ensemble. Le pain croque.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4470,7 @@
 papa|Bravo.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4806,7 @@
           <t>narrateur|L'assiette verte est près de maman. Nora est assise. À table, ensemble, elle mange son morceau.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5116,6 +5143,7 @@
 maman|On reste assis jusqu'à la fin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5307,6 +5335,7 @@
           <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5474,6 +5503,7 @@
           <t>narrateur|Le fromage est dans l'assiette bleue. Nora est assise à table. Ils mangent ensemble. Puis ils rangent.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5641,6 +5671,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5808,6 +5839,7 @@
           <t>narrateur|L'assiette rouge sent le fromage. Nora reste assise. Ensemble, à table, c'est calme.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5975,6 +6007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6143,6 +6176,7 @@
 enfant-f|J'étais assise.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6310,6 +6344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6477,6 +6512,7 @@
           <t>narrateur|Nora choisit la chaise près de maman. La nappe est douce. Elle s'assoit. Les fesses sur la chaise. Maman s'assoit à côté. Papa en face. Ils mangent ensemble à table. Nora tient sa fourchette. Elle reste assise.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6660,6 +6696,7 @@
           <t>narrateur|Nora est près de maman. Que fait-elle pour manger ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6831,6 +6868,7 @@
           <t>narrateur|Près de maman, Nora est assise. La table les tient ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7022,6 +7060,7 @@
           <t>narrateur|On peut prendre la soupe, le pain, ou le fromage.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7189,6 +7228,7 @@
           <t>narrateur|Maman goûte la soupe. Nora est assise à côté. Elle mange à table, ensemble. Une goutte tombe. Maman l'essuie. Nora reste sur sa chaise.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7380,6 +7420,7 @@
           <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7547,6 +7588,7 @@
           <t>narrateur|L'assiette bleue fume un peu. Nora est assise à table, ensemble. Elle souffle.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7714,6 +7756,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7881,6 +7924,7 @@
           <t>narrateur|L'assiette rouge est près de maman. Nora reste assise. Ils mangent ensemble à table.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8048,6 +8092,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8215,6 +8260,7 @@
           <t>narrateur|L'assiette verte attend la cuillère. Nora est assise. Ensemble, à table, c'est bon.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8382,6 +8428,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8550,6 +8597,7 @@
 maman|Les fesses sur la chaise.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8741,6 +8789,7 @@
           <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8908,6 +8957,7 @@
           <t>narrateur|Le pain est sur l'assiette bleue. Nora est assise à table. Ils mangent ensemble. Des miettes. On les ramasse.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9075,6 +9125,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9242,6 +9293,7 @@
           <t>narrateur|L'assiette rouge a des miettes. Nora reste assise. Ensemble, à table, elle mange.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9409,6 +9461,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9576,6 +9629,7 @@
           <t>narrateur|L'assiette verte est propre. Nora est assise. Ils mangent le pain ensemble à table.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9743,6 +9797,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9911,6 +9966,7 @@
 papa|On est tous assis.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10102,6 +10158,7 @@
           <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10269,6 +10326,7 @@
           <t>narrateur|L'assiette bleue a un petit bout. Nora est assise à table, ensemble. Elle dit merci.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10436,6 +10494,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10603,6 +10662,7 @@
           <t>narrateur|L'assiette rouge sent bon. Nora reste assise. Ils mangent ensemble à table.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10770,6 +10830,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10937,6 +10998,7 @@
           <t>narrateur|L'assiette verte est au milieu. Nora est assise. À table, ensemble, le repas se termine.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11104,6 +11166,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11272,6 +11335,7 @@
 enfant-f|Je suis assise. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11455,6 +11519,7 @@
           <t>narrateur|Nora a sa petite chaise. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11626,6 +11691,7 @@
           <t>narrateur|La petite chaise est stable. Nora est assise. Toute la famille est ensemble à table.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11817,6 +11883,7 @@
           <t>narrateur|On peut prendre la soupe, le pain, ou le fromage.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11984,6 +12051,7 @@
           <t>narrateur|La soupe arrive. Nora, sur sa petite chaise, reste assise. Elle mange à table, ensemble. La cuillère est à sa taille.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12175,6 +12243,7 @@
           <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12342,6 +12411,7 @@
           <t>narrateur|L'assiette bleue est petite aussi. Nora est assise à table. Ils mangent ensemble.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12509,6 +12579,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12676,6 +12747,7 @@
           <t>narrateur|L'assiette rouge va bien avec la chaise. Nora reste assise. Ensemble, à table, elle finit sa cuillère.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12843,6 +12915,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13010,6 +13083,7 @@
           <t>narrateur|L'assiette verte est ronde. Nora est assise. Ils mangent ensemble à table. Papa range.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13177,6 +13251,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13345,6 +13420,7 @@
 maman|Bien.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13536,6 +13612,7 @@
           <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13703,6 +13780,7 @@
           <t>narrateur|Le pain rejoint l'assiette bleue. Nora est assise à table, ensemble. Une miette tombe. Elle la pose.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13870,6 +13948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14037,6 +14116,7 @@
           <t>narrateur|L'assiette rouge attend. Nora reste assise. Ils mangent le pain ensemble à table.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14204,6 +14284,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14371,6 +14452,7 @@
           <t>narrateur|L'assiette verte a une miette. Nora est assise. À table, ensemble, c'est fini.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14538,6 +14620,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14705,6 +14788,7 @@
           <t>narrateur|Papa glisse un bout de fromage. Nora est assise. Elle mange à table, ensemble. Elle reste jusqu'au bout, sur sa petite chaise.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14896,6 +14980,7 @@
           <t>narrateur|On peut prendre bleue, rouge, ou verte.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15063,6 +15148,7 @@
           <t>narrateur|L'assiette bleue est vide, presque. Nora est assise à table. Ils étaient ensemble.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15230,6 +15316,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15397,6 +15484,7 @@
           <t>narrateur|L'assiette rouge a encore une odeur. Nora reste assise. Ensemble, à table, elle dit merci.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15564,6 +15652,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15731,6 +15820,7 @@
           <t>narrateur|L'assiette verte rentre dans le placard. Nora était assise. Ils ont mangé ensemble à table.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15898,6 +15988,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15916,7 +16007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15940,6 +16031,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15954,7 +16059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16141,6 +16246,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
